--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2021_atacama.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2021_atacama.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>877890.62</v>
+        <v>877890.63</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>795057.75</v>
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1079213.62</v>
+        <v>1079213.63</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>976086</v>
@@ -579,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1130022.62</v>
+        <v>1130022.63</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1020703.44</v>
@@ -604,7 +604,7 @@
         <v>1288952</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1344507.62</v>
+        <v>1344507.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>1220936</v>
